--- a/Daywise_Distance_March_2026.xlsx
+++ b/Daywise_Distance_March_2026.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6D39FC-6673-4F20-8DD4-5B7D5BDB38E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Daywise Distance" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Daywise Distance" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -131,6 +130,9 @@
     <t>1618 TP</t>
   </si>
   <si>
+    <t>JC 400 MH 15 JM 1383 - SWEEPER MACHINE</t>
+  </si>
+  <si>
     <t>ELGIN</t>
   </si>
   <si>
@@ -144,22 +146,19 @@
   </si>
   <si>
     <t>General</t>
-  </si>
-  <si>
-    <t>JC 400 MH 15 JM 1383 - SWEEPER MACHINE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -172,8 +171,8 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFF0000"/>
       <sz val="8"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -592,12 +591,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -606,7 +605,7 @@
     <col min="5" max="35" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="28.05" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -713,7 +712,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="48" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -724,7 +723,7 @@
         <v>37</v>
       </c>
       <c r="D2" s="3">
-        <v>1779</v>
+        <v>1082</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="3">
@@ -808,15 +807,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="48" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" s="3">
         <v>1234</v>
@@ -903,15 +902,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="48" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="D4" s="3">
         <v>1201</v>
@@ -996,18 +995,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="48" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3">
-        <v>1088</v>
+        <v>1114</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3">
@@ -1089,6 +1088,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>